--- a/data/dim_funcionarios.xlsx
+++ b/data/dim_funcionarios.xlsx
@@ -533,11 +533,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>503617760</t>
+          <t>503638393</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>32703</v>
+        <v>24409</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Auxiliar de Limpeza</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,20 +565,20 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>44222</v>
+        <v>43678</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>1776.41</v>
+        <v>1969.63</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.0146</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>86522.23</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -610,11 +610,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>857368875</t>
+          <t>613111173</t>
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>30518</v>
+        <v>37276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>45490</v>
+        <v>45071</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>2179.29</v>
+        <v>4746.45</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0382</v>
+        <v>0.0066</v>
       </c>
       <c r="P3" t="n">
-        <v>28845.77</v>
+        <v>64928.19</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -687,11 +687,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>367822390</t>
+          <t>223322124</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>26559</v>
+        <v>34257</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Estoquista</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -719,20 +719,20 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>45535</v>
+        <v>43893</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>2046.44</v>
+        <v>1783.62</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.0365</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>91917.89999999999</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -764,11 +764,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>247890868</t>
+          <t>235150845</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>31483</v>
+        <v>37190</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -796,20 +796,20 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>45549</v>
+        <v>45376</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>1704.94</v>
+        <v>5720.26</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0119</v>
+        <v>0.0053</v>
       </c>
       <c r="P5" t="n">
-        <v>53150.25</v>
+        <v>62061.75</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -841,11 +841,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>822753647</t>
+          <t>76493338</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>37571</v>
+        <v>26132</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -873,20 +873,20 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>44427</v>
+        <v>43884</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>2272.03</v>
+        <v>2052.41</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>84116.05</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -918,11 +918,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>870779462</t>
+          <t>896875091</t>
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>28471</v>
+        <v>34369</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -950,20 +950,20 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>43959</v>
+        <v>45580</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>1902.05</v>
+        <v>4659.38</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0273</v>
+        <v>0.0146</v>
       </c>
       <c r="P7" t="n">
-        <v>45048.06</v>
+        <v>62969.62</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -995,11 +995,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>212917840</t>
+          <t>280245167</t>
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>37448</v>
+        <v>35609</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1027,14 +1027,14 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>44050</v>
+        <v>45549</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>2123.73</v>
+        <v>1997.91</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>874195155</t>
+          <t>905588234</t>
         </is>
       </c>
       <c r="E9" s="1" t="n">
-        <v>25758</v>
+        <v>28493</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1104,16 +1104,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>45291</v>
+        <v>44851</v>
       </c>
       <c r="M9" s="1" t="n">
-        <v>45499</v>
+        <v>45042</v>
       </c>
       <c r="N9" t="n">
-        <v>1658.07</v>
+        <v>1678.7</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>247740381</t>
+          <t>822753647</t>
         </is>
       </c>
       <c r="E10" s="1" t="n">
-        <v>23773</v>
+        <v>37571</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1183,14 +1183,14 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>43754</v>
+        <v>44427</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>1537.36</v>
+        <v>1725.35</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1228,11 +1228,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>755849623</t>
+          <t>139153910</t>
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>31635</v>
+        <v>28471</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1260,22 +1260,22 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>45276</v>
+        <v>43959</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>45913</v>
+        <v>44367</v>
       </c>
       <c r="N11" t="n">
-        <v>1858.25</v>
+        <v>1902.05</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0117</v>
+        <v>0.0223</v>
       </c>
       <c r="P11" t="n">
-        <v>94779.73</v>
+        <v>45048.06</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1307,11 +1307,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>803632351</t>
+          <t>444722678</t>
         </is>
       </c>
       <c r="E12" s="1" t="n">
-        <v>32947</v>
+        <v>23982</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Subgerente</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>45139</v>
+        <v>44050</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>45465</v>
+        <v>45557</v>
       </c>
       <c r="N12" t="n">
-        <v>1922.06</v>
+        <v>3860.23</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>51503.85</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1386,11 +1386,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>346775035</t>
+          <t>190357087</t>
         </is>
       </c>
       <c r="E13" s="1" t="n">
-        <v>28226</v>
+        <v>29113</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Subgerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1418,20 +1418,20 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>43569</v>
+        <v>43219</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>3255.68</v>
+        <v>2086.88</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>32472.69</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>475575877</t>
+          <t>552066815</t>
         </is>
       </c>
       <c r="E14" s="1" t="n">
-        <v>36684</v>
+        <v>26569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Estoquista</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1495,20 +1495,20 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>43836</v>
+        <v>45606</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>2194.32</v>
+        <v>4689.49</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>82193.64999999999</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1540,11 +1540,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>98910632</t>
+          <t>295596583</t>
         </is>
       </c>
       <c r="E15" s="1" t="n">
-        <v>29419</v>
+        <v>36775</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Segurança</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1572,20 +1572,20 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>44053</v>
+        <v>43609</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>2087.53</v>
+        <v>2235.9</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0248</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>71955.12</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1617,11 +1617,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>768325966</t>
+          <t>76123284</t>
         </is>
       </c>
       <c r="E16" s="1" t="n">
-        <v>34939</v>
+        <v>31518</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Segurança</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1649,20 +1649,20 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>43441</v>
+        <v>45139</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>1740.41</v>
+        <v>2034.35</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.0203</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>53784.04</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1694,11 +1694,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>396628748</t>
+          <t>65689684</t>
         </is>
       </c>
       <c r="E17" s="1" t="n">
-        <v>30745</v>
+        <v>25658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Nutricionista</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1726,20 +1726,20 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>44060</v>
+        <v>44947</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>6058.82</v>
+        <v>3252.47</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0183</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>72325.61</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1771,11 +1771,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>498159595</t>
+          <t>475575877</t>
         </is>
       </c>
       <c r="E18" s="1" t="n">
-        <v>35154</v>
+        <v>36684</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Repositor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1803,20 +1803,20 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>45910</v>
+        <v>43836</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>1775.58</v>
+        <v>5665.26</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.0118</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>61483.18</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1848,11 +1848,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>219917843</t>
+          <t>173272381</t>
         </is>
       </c>
       <c r="E19" s="1" t="n">
-        <v>29869</v>
+        <v>34791</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1880,14 +1880,14 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>45975</v>
+        <v>44053</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>1996.63</v>
+        <v>1767.29</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1925,11 +1925,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>125370201</t>
+          <t>276150799</t>
         </is>
       </c>
       <c r="E20" s="1" t="n">
-        <v>29721</v>
+        <v>36817</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Auxiliar de Limpeza</t>
+          <t>Subgerente</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1957,14 +1957,14 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>45133</v>
+        <v>43196</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>1535.48</v>
+        <v>3241.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>483648982</t>
+          <t>732099047</t>
         </is>
       </c>
       <c r="E21" s="1" t="n">
-        <v>31699</v>
+        <v>31117</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Estoquista</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2034,16 +2034,16 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>45897</v>
+        <v>43819</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>45991</v>
+        <v>45282</v>
       </c>
       <c r="N21" t="n">
-        <v>2387.24</v>
+        <v>1795.64</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2081,11 +2081,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>564198242</t>
+          <t>862621910</t>
         </is>
       </c>
       <c r="E22" s="1" t="n">
-        <v>29861</v>
+        <v>29753</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Nutricionista</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2116,17 +2116,17 @@
         <v>2</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>45948</v>
+        <v>46007</v>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>1914.76</v>
+        <v>4697.21</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0261</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>94575.95</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2158,11 +2158,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47146583</t>
+          <t>429528441</t>
         </is>
       </c>
       <c r="E23" s="1" t="n">
-        <v>27842</v>
+        <v>35154</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2190,20 +2190,20 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>45236</v>
+        <v>45512</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>1853.58</v>
+        <v>1775.58</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0386</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>57308.89</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2235,11 +2235,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>450083557</t>
+          <t>429427878</t>
         </is>
       </c>
       <c r="E24" s="1" t="n">
-        <v>29944</v>
+        <v>32439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Auxiliar de Limpeza</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2267,20 +2267,20 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>44330</v>
+        <v>45975</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>1597.29</v>
+        <v>2115.11</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>59014.89</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2312,11 +2312,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>615070230</t>
+          <t>483648982</t>
         </is>
       </c>
       <c r="E25" s="1" t="n">
-        <v>28362</v>
+        <v>31699</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2344,20 +2344,20 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>45704</v>
+        <v>45897</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>1775.25</v>
+        <v>5713.7</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0242</v>
+        <v>0.0065</v>
       </c>
       <c r="P25" t="n">
-        <v>54360.24</v>
+        <v>148644.83</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2389,11 +2389,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>486695938</t>
+          <t>564198242</t>
         </is>
       </c>
       <c r="E26" s="1" t="n">
-        <v>33548</v>
+        <v>29861</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2421,20 +2421,20 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>43124</v>
+        <v>45359</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>1883.78</v>
+        <v>5498.89</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0208</v>
+        <v>0.0184</v>
       </c>
       <c r="P26" t="n">
-        <v>95717.75999999999</v>
+        <v>101930.73</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2466,11 +2466,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>268904273</t>
+          <t>888862735</t>
         </is>
       </c>
       <c r="E27" s="1" t="n">
-        <v>32722</v>
+        <v>36339</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Estoquista</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2498,20 +2498,20 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>43394</v>
+        <v>45236</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>1970.39</v>
+        <v>2289.12</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0321</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>78942.09</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2543,11 +2543,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>286886466</t>
+          <t>513582441</t>
         </is>
       </c>
       <c r="E28" s="1" t="n">
-        <v>33426</v>
+        <v>34208</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Subgerente</t>
+          <t>Segurança</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2575,14 +2575,14 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>45918</v>
+        <v>44668</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>3934.22</v>
+        <v>2129.34</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2620,11 +2620,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>840829979</t>
+          <t>729424763</t>
         </is>
       </c>
       <c r="E29" s="1" t="n">
-        <v>31425</v>
+        <v>31389</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2652,20 +2652,20 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>44932</v>
+        <v>45206</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>2190.5</v>
+        <v>5355.18</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0311</v>
+        <v>0.007</v>
       </c>
       <c r="P29" t="n">
-        <v>80421.17999999999</v>
+        <v>111518.65</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2697,11 +2697,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>385721680</t>
+          <t>62086051</t>
         </is>
       </c>
       <c r="E30" s="1" t="n">
-        <v>37446</v>
+        <v>31110</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2729,20 +2729,20 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>43490</v>
+        <v>43626</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>1852.14</v>
+        <v>1880.47</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0149</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>37955.9</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2774,11 +2774,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>235524693</t>
+          <t>448025650</t>
         </is>
       </c>
       <c r="E31" s="1" t="n">
-        <v>29822</v>
+        <v>23984</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Segurança</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2806,14 +2806,14 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>43214</v>
+        <v>44714</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>1826.09</v>
+        <v>2171.45</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2851,11 +2851,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>866387574</t>
+          <t>268904273</t>
         </is>
       </c>
       <c r="E32" s="1" t="n">
-        <v>29427</v>
+        <v>32722</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2883,20 +2883,20 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>45251</v>
+        <v>43394</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>1788.15</v>
+        <v>1970.39</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0382</v>
+        <v>0.0321</v>
       </c>
       <c r="P32" t="n">
-        <v>71117.86</v>
+        <v>78942.09</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2928,11 +2928,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>54484813</t>
+          <t>209897545</t>
         </is>
       </c>
       <c r="E33" s="1" t="n">
-        <v>32275</v>
+        <v>26344</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Subgerente</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2960,20 +2960,20 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>44798</v>
+        <v>45918</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>3551.47</v>
+        <v>5923.1</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>80277.12</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -3005,11 +3005,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>12298064</t>
+          <t>721381981</t>
         </is>
       </c>
       <c r="E34" s="1" t="n">
-        <v>29376</v>
+        <v>27940</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3037,20 +3037,20 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>44176</v>
+        <v>43628</v>
       </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>2166.42</v>
+        <v>4888.39</v>
       </c>
       <c r="O34" t="n">
-        <v>0.0369</v>
+        <v>0.0129</v>
       </c>
       <c r="P34" t="n">
-        <v>150070.81</v>
+        <v>83060.95</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -3082,11 +3082,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>363830626</t>
+          <t>178706888</t>
         </is>
       </c>
       <c r="E35" s="1" t="n">
-        <v>24736</v>
+        <v>33312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Segurança</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3114,14 +3114,14 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>43469</v>
+        <v>44516</v>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>2189.35</v>
+        <v>1747.98</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3159,11 +3159,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>131619115</t>
+          <t>132162242</t>
         </is>
       </c>
       <c r="E36" s="1" t="n">
-        <v>35124</v>
+        <v>24551</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3191,20 +3191,20 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>43103</v>
+        <v>43214</v>
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>1987.78</v>
+        <v>1848.09</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>0.0116</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>152029.6</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -3236,11 +3236,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>204267928</t>
+          <t>425093543</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>29089</v>
+        <v>33522</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Subgerente</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3268,20 +3268,20 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>45583</v>
+        <v>44689</v>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>4991.73</v>
+        <v>3644.1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.0078</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>45033.29</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -3313,11 +3313,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>256880109</t>
+          <t>510965371</t>
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>31167</v>
+        <v>29696</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3345,20 +3345,20 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>44132</v>
+        <v>44798</v>
       </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>5217.48</v>
+        <v>1922.36</v>
       </c>
       <c r="O38" t="n">
-        <v>0.0163</v>
+        <v>0.0103</v>
       </c>
       <c r="P38" t="n">
-        <v>35191.19</v>
+        <v>145790.07</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -3390,11 +3390,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>826189809</t>
+          <t>329667377</t>
         </is>
       </c>
       <c r="E39" s="1" t="n">
-        <v>28689</v>
+        <v>30562</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3422,20 +3422,20 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>45993</v>
+        <v>44638</v>
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>2187.27</v>
+        <v>1930.8</v>
       </c>
       <c r="O39" t="n">
-        <v>0.0262</v>
+        <v>0.0223</v>
       </c>
       <c r="P39" t="n">
-        <v>38385.28</v>
+        <v>103621.65</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -3467,11 +3467,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>34449855</t>
+          <t>448566914</t>
         </is>
       </c>
       <c r="E40" s="1" t="n">
-        <v>34601</v>
+        <v>24426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Repositor</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3499,20 +3499,20 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>45665</v>
+        <v>43182</v>
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>2032.94</v>
+        <v>2091.65</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>0.0263</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>67250.82000000001</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3544,11 +3544,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>333491875</t>
+          <t>204267928</t>
         </is>
       </c>
       <c r="E41" s="1" t="n">
-        <v>24647</v>
+        <v>29089</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Estoquista</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3576,20 +3576,20 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>44553</v>
+        <v>45583</v>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>2335.63</v>
+        <v>1822.42</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>45033.29</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>202264603</t>
+          <t>256880109</t>
         </is>
       </c>
       <c r="E42" s="1" t="n">
-        <v>35698</v>
+        <v>31167</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3653,20 +3653,20 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>44809</v>
+        <v>44132</v>
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>2234.75</v>
+        <v>1892.96</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>0.0325</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>35191.19</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -3698,11 +3698,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>926489793</t>
+          <t>178973226</t>
         </is>
       </c>
       <c r="E43" s="1" t="n">
-        <v>36674</v>
+        <v>28141</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3730,22 +3730,20 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>43932</v>
-      </c>
-      <c r="M43" s="1" t="n">
-        <v>45366</v>
-      </c>
+        <v>45993</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>1866.11</v>
+        <v>2144.54</v>
       </c>
       <c r="O43" t="n">
-        <v>0.0165</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>49514.77</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3757,7 +3755,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Inativo</t>
+          <t>Ativo</t>
         </is>
       </c>
     </row>
@@ -3777,11 +3775,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>33128716</t>
+          <t>17643182</t>
         </is>
       </c>
       <c r="E44" s="1" t="n">
-        <v>23974</v>
+        <v>34099</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3800,7 +3798,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Subgerente</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3809,20 +3807,20 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>44106</v>
+        <v>45218</v>
       </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
-        <v>5956.85</v>
+        <v>4267.5</v>
       </c>
       <c r="O44" t="n">
-        <v>0.0077</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>127887.2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3854,11 +3852,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>154590933</t>
+          <t>92033599</t>
         </is>
       </c>
       <c r="E45" s="1" t="n">
-        <v>35771</v>
+        <v>25195</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3877,7 +3875,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Repositor</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3886,22 +3884,22 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>43591</v>
+        <v>43932</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>45391</v>
+        <v>44640</v>
       </c>
       <c r="N45" t="n">
-        <v>1806.52</v>
+        <v>2178.69</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>109015.14</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3933,11 +3931,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>849010459</t>
+          <t>391333171</t>
         </is>
       </c>
       <c r="E46" s="1" t="n">
-        <v>32832</v>
+        <v>32713</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3956,7 +3954,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Subgerente</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3965,20 +3963,20 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L46" s="1" t="n">
-        <v>43975</v>
+        <v>44809</v>
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>3441.09</v>
+        <v>6085.05</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>0.0057</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>97485.8</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -4010,11 +4008,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>330502860</t>
+          <t>363111811</t>
         </is>
       </c>
       <c r="E47" s="1" t="n">
-        <v>25094</v>
+        <v>30010</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4033,7 +4031,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Estoquista</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4042,20 +4040,20 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>43252</v>
+        <v>44702</v>
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>1947</v>
+        <v>4866.7</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>0.0142</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>27588.34</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -4087,11 +4085,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>292758271</t>
+          <t>554194550</t>
         </is>
       </c>
       <c r="E48" s="1" t="n">
-        <v>33833</v>
+        <v>28329</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4110,7 +4108,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4119,20 +4117,20 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>43862</v>
+        <v>43332</v>
       </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>5460.55</v>
+        <v>2195.84</v>
       </c>
       <c r="O48" t="n">
-        <v>0.0166</v>
+        <v>0.0253</v>
       </c>
       <c r="P48" t="n">
-        <v>104847.02</v>
+        <v>50251.59</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -4164,11 +4162,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>365317299</t>
+          <t>849010459</t>
         </is>
       </c>
       <c r="E49" s="1" t="n">
-        <v>27185</v>
+        <v>32832</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4196,20 +4194,20 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>45343</v>
+        <v>44791</v>
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>1873.92</v>
+        <v>1792.73</v>
       </c>
       <c r="O49" t="n">
-        <v>0.0355</v>
+        <v>0.0175</v>
       </c>
       <c r="P49" t="n">
-        <v>91105.17999999999</v>
+        <v>128346.25</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -4241,11 +4239,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>691134032</t>
+          <t>321836843</t>
         </is>
       </c>
       <c r="E50" s="1" t="n">
-        <v>26750</v>
+        <v>29267</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4264,7 +4262,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4273,20 +4271,20 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L50" s="1" t="n">
-        <v>43356</v>
+        <v>44452</v>
       </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>2078.6</v>
+        <v>1804.83</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0209</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>129389.08</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -4318,11 +4316,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>388468265</t>
+          <t>603897322</t>
         </is>
       </c>
       <c r="E51" s="1" t="n">
-        <v>34224</v>
+        <v>25102</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4341,7 +4339,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4350,20 +4348,20 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L51" s="1" t="n">
-        <v>44509</v>
+        <v>44822</v>
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>1873.83</v>
+        <v>1995.73</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>0.0167</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>145999.58</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -4395,11 +4393,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>743860645</t>
+          <t>840655465</t>
         </is>
       </c>
       <c r="E52" s="1" t="n">
-        <v>25920</v>
+        <v>36939</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4418,7 +4416,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Subgerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4427,20 +4425,20 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L52" s="1" t="n">
-        <v>44832</v>
+        <v>43200</v>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>3263.27</v>
+        <v>1944.83</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>108032.27</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -4472,11 +4470,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>706402001</t>
+          <t>493378625</t>
         </is>
       </c>
       <c r="E53" s="1" t="n">
-        <v>27593</v>
+        <v>24463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4495,7 +4493,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Nutricionista</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4504,20 +4502,20 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L53" s="1" t="n">
-        <v>45097</v>
+        <v>43356</v>
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>2106.61</v>
+        <v>3857.81</v>
       </c>
       <c r="O53" t="n">
-        <v>0.0118</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>79007.14</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -4549,11 +4547,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>659525221</t>
+          <t>40894659</t>
         </is>
       </c>
       <c r="E54" s="1" t="n">
-        <v>26855</v>
+        <v>31689</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4572,7 +4570,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4581,20 +4579,20 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>44556</v>
+        <v>44779</v>
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>1933.98</v>
+        <v>1845.65</v>
       </c>
       <c r="O54" t="n">
-        <v>0.0278</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>152700.35</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -4626,11 +4624,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>62630789</t>
+          <t>353300142</t>
         </is>
       </c>
       <c r="E55" s="1" t="n">
-        <v>37810</v>
+        <v>36145</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4649,7 +4647,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Segurança</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4661,11 +4659,11 @@
         <v>9</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>43661</v>
+        <v>45390</v>
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>2110.36</v>
+        <v>1864.08</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -4703,11 +4701,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>575060498</t>
+          <t>820248140</t>
         </is>
       </c>
       <c r="E56" s="1" t="n">
-        <v>37749</v>
+        <v>28333</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4726,7 +4724,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4735,22 +4733,22 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>44699</v>
+        <v>45278</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>45733</v>
+        <v>45924</v>
       </c>
       <c r="N56" t="n">
-        <v>1893.83</v>
+        <v>5259.43</v>
       </c>
       <c r="O56" t="n">
-        <v>0.0304</v>
+        <v>0.0057</v>
       </c>
       <c r="P56" t="n">
-        <v>45224.48</v>
+        <v>118288.44</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -4782,11 +4780,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>462041786</t>
+          <t>785865775</t>
         </is>
       </c>
       <c r="E57" s="1" t="n">
-        <v>33124</v>
+        <v>33132</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4805,7 +4803,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Auxiliar de Limpeza</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4817,11 +4815,11 @@
         <v>9</v>
       </c>
       <c r="L57" s="1" t="n">
-        <v>45676</v>
+        <v>44306</v>
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
-        <v>2032.01</v>
+        <v>1502.93</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -4859,11 +4857,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>400131758</t>
+          <t>808941744</t>
         </is>
       </c>
       <c r="E58" s="1" t="n">
-        <v>33348</v>
+        <v>29124</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4882,7 +4880,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Auxiliar de Limpeza</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4891,22 +4889,22 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L58" s="1" t="n">
-        <v>43646</v>
+        <v>45593</v>
       </c>
       <c r="M58" s="1" t="n">
-        <v>45829</v>
+        <v>45970</v>
       </c>
       <c r="N58" t="n">
-        <v>2166.11</v>
+        <v>1650.76</v>
       </c>
       <c r="O58" t="n">
-        <v>0.0145</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>85763.67</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -4938,11 +4936,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>573758796</t>
+          <t>538228930</t>
         </is>
       </c>
       <c r="E59" s="1" t="n">
-        <v>27670</v>
+        <v>32849</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4970,20 +4968,20 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L59" s="1" t="n">
-        <v>44513</v>
+        <v>44699</v>
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
-        <v>1795.45</v>
+        <v>2065.31</v>
       </c>
       <c r="O59" t="n">
-        <v>0.0109</v>
+        <v>0.0327</v>
       </c>
       <c r="P59" t="n">
-        <v>126575.61</v>
+        <v>153566.48</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -5015,11 +5013,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>379612730</t>
+          <t>44232847</t>
         </is>
       </c>
       <c r="E60" s="1" t="n">
-        <v>27333</v>
+        <v>30969</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5047,14 +5045,14 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L60" s="1" t="n">
-        <v>44974</v>
+        <v>43157</v>
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
-        <v>1825.68</v>
+        <v>2034.93</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -5092,11 +5090,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>411124180</t>
+          <t>369699242</t>
         </is>
       </c>
       <c r="E61" s="1" t="n">
-        <v>36328</v>
+        <v>36077</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5115,7 +5113,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Segurança</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5124,20 +5122,20 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L61" s="1" t="n">
-        <v>45618</v>
+        <v>43646</v>
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
-        <v>2123.61</v>
+        <v>4646.95</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>0.0161</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>92824.25999999999</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -5169,11 +5167,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>17962674</t>
+          <t>573758796</t>
         </is>
       </c>
       <c r="E62" s="1" t="n">
-        <v>29281</v>
+        <v>27670</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5192,7 +5190,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Auxiliar de Limpeza</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5201,20 +5199,20 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L62" s="1" t="n">
-        <v>43226</v>
+        <v>44513</v>
       </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
-        <v>1500.37</v>
+        <v>1795.45</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>0.0109</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>126575.61</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -5246,11 +5244,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>58897713</t>
+          <t>379612730</t>
         </is>
       </c>
       <c r="E63" s="1" t="n">
-        <v>34652</v>
+        <v>27333</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5269,7 +5267,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Estoquista</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5278,20 +5276,20 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>44500</v>
+        <v>44974</v>
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
-        <v>1877.4</v>
+        <v>1929.96</v>
       </c>
       <c r="O63" t="n">
-        <v>0.0232</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>122078.77</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -5323,11 +5321,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>790133100</t>
+          <t>162957225</t>
         </is>
       </c>
       <c r="E64" s="1" t="n">
-        <v>24266</v>
+        <v>25112</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5346,7 +5344,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5355,20 +5353,22 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>45999</v>
-      </c>
-      <c r="M64" t="inlineStr"/>
+        <v>45618</v>
+      </c>
+      <c r="M64" s="1" t="n">
+        <v>46011</v>
+      </c>
       <c r="N64" t="n">
-        <v>6047.4</v>
+        <v>1984.52</v>
       </c>
       <c r="O64" t="n">
-        <v>0.0119</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>131892.77</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
     </row>
@@ -5400,11 +5400,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>337264146</t>
+          <t>301473085</t>
         </is>
       </c>
       <c r="E65" s="1" t="n">
-        <v>24947</v>
+        <v>28309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Repositor</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5435,17 +5435,17 @@
         <v>8</v>
       </c>
       <c r="L65" s="1" t="n">
-        <v>45209</v>
+        <v>43226</v>
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
-        <v>1830.39</v>
+        <v>1919.95</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>0.0101</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>127786.96</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -5477,11 +5477,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>219976936</t>
+          <t>335274874</t>
         </is>
       </c>
       <c r="E66" s="1" t="n">
-        <v>32847</v>
+        <v>26641</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Segurança</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5509,22 +5509,22 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L66" s="1" t="n">
-        <v>43365</v>
+        <v>44604</v>
       </c>
       <c r="M66" s="1" t="n">
-        <v>44518</v>
+        <v>45131</v>
       </c>
       <c r="N66" t="n">
-        <v>2025.36</v>
+        <v>1734.77</v>
       </c>
       <c r="O66" t="n">
-        <v>0.0233</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>152541.47</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -5556,11 +5556,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>846886495</t>
+          <t>225609742</t>
         </is>
       </c>
       <c r="E67" s="1" t="n">
-        <v>35784</v>
+        <v>26696</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5588,20 +5588,20 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L67" s="1" t="n">
-        <v>44546</v>
+        <v>43624</v>
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
-        <v>1786.71</v>
+        <v>1894.74</v>
       </c>
       <c r="O67" t="n">
-        <v>0.0346</v>
+        <v>0.019</v>
       </c>
       <c r="P67" t="n">
-        <v>128555.35</v>
+        <v>47460.56</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -5633,11 +5633,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>394490985</t>
+          <t>507091271</t>
         </is>
       </c>
       <c r="E68" s="1" t="n">
-        <v>31476</v>
+        <v>32847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Nutricionista</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5665,22 +5665,22 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L68" s="1" t="n">
-        <v>43521</v>
+        <v>45461</v>
       </c>
       <c r="M68" s="1" t="n">
-        <v>45319</v>
+        <v>45815</v>
       </c>
       <c r="N68" t="n">
-        <v>3387.49</v>
+        <v>2025.36</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>0.0384</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>152541.47</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -5712,11 +5712,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>928021336</t>
+          <t>798365643</t>
         </is>
       </c>
       <c r="E69" s="1" t="n">
-        <v>32103</v>
+        <v>31902</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Repositor</t>
+          <t>Subgerente</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5744,16 +5744,16 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L69" s="1" t="n">
-        <v>44832</v>
+        <v>44546</v>
       </c>
       <c r="M69" s="1" t="n">
-        <v>45214</v>
+        <v>44724</v>
       </c>
       <c r="N69" t="n">
-        <v>1803.65</v>
+        <v>3580.04</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -5791,11 +5791,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>752589860</t>
+          <t>767201021</t>
         </is>
       </c>
       <c r="E70" s="1" t="n">
-        <v>29765</v>
+        <v>30953</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5823,20 +5823,20 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L70" s="1" t="n">
-        <v>45164</v>
+        <v>43252</v>
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
-        <v>2259.01</v>
+        <v>2077.65</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>0.0144</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>113208.78</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -5868,11 +5868,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>297563050</t>
+          <t>67358122</t>
         </is>
       </c>
       <c r="E71" s="1" t="n">
-        <v>30460</v>
+        <v>29570</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5900,14 +5900,14 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L71" s="1" t="n">
-        <v>45682</v>
+        <v>44099</v>
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>1974.29</v>
+        <v>1953.63</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -5945,11 +5945,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>836200712</t>
+          <t>245871616</t>
         </is>
       </c>
       <c r="E72" s="1" t="n">
-        <v>28121</v>
+        <v>38094</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5977,20 +5977,20 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L72" s="1" t="n">
-        <v>44081</v>
+        <v>43269</v>
       </c>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
-        <v>6125.51</v>
+        <v>2161.45</v>
       </c>
       <c r="O72" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0185</v>
       </c>
       <c r="P72" t="n">
-        <v>47387.53</v>
+        <v>50326.54</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -6022,11 +6022,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>606096742</t>
+          <t>26259605</t>
         </is>
       </c>
       <c r="E73" s="1" t="n">
-        <v>30478</v>
+        <v>31209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6054,20 +6054,20 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L73" s="1" t="n">
-        <v>45711</v>
+        <v>45468</v>
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
-        <v>2210.81</v>
+        <v>1787.98</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>0.0288</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>45825.76</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -6099,11 +6099,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>632760134</t>
+          <t>836200712</t>
         </is>
       </c>
       <c r="E74" s="1" t="n">
-        <v>31878</v>
+        <v>28121</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6131,20 +6131,20 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L74" s="1" t="n">
-        <v>45318</v>
+        <v>44081</v>
       </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="n">
-        <v>1777.69</v>
+        <v>2176.72</v>
       </c>
       <c r="O74" t="n">
-        <v>0.0229</v>
+        <v>0.0175</v>
       </c>
       <c r="P74" t="n">
-        <v>117256.66</v>
+        <v>47387.53</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -6176,11 +6176,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>227301702</t>
+          <t>606096742</t>
         </is>
       </c>
       <c r="E75" s="1" t="n">
-        <v>31946</v>
+        <v>30478</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6208,20 +6208,20 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L75" s="1" t="n">
-        <v>43203</v>
+        <v>45711</v>
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>2048.51</v>
+        <v>2042.34</v>
       </c>
       <c r="O75" t="n">
-        <v>0.0277</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>68389.27</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -6253,11 +6253,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>957322294</t>
+          <t>944990562</t>
         </is>
       </c>
       <c r="E76" s="1" t="n">
-        <v>35353</v>
+        <v>30958</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6285,22 +6285,22 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L76" s="1" t="n">
-        <v>43271</v>
+        <v>45318</v>
       </c>
       <c r="M76" s="1" t="n">
-        <v>45178</v>
+        <v>45570</v>
       </c>
       <c r="N76" t="n">
-        <v>2177.61</v>
+        <v>2041.69</v>
       </c>
       <c r="O76" t="n">
-        <v>0.0218</v>
+        <v>0.0293</v>
       </c>
       <c r="P76" t="n">
-        <v>142900.64</v>
+        <v>132581.86</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -6332,11 +6332,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>808584332</t>
+          <t>227301702</t>
         </is>
       </c>
       <c r="E77" s="1" t="n">
-        <v>30897</v>
+        <v>31946</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Estoquista</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6364,14 +6364,14 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L77" s="1" t="n">
-        <v>45748</v>
+        <v>43106</v>
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
-        <v>2570.01</v>
+        <v>2218.22</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -6409,11 +6409,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>98088158</t>
+          <t>659801898</t>
         </is>
       </c>
       <c r="E78" s="1" t="n">
-        <v>23984</v>
+        <v>29551</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Auxiliar de Limpeza</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6441,22 +6441,22 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L78" s="1" t="n">
-        <v>43278</v>
+        <v>44814</v>
       </c>
       <c r="M78" s="1" t="n">
-        <v>43883</v>
+        <v>45330</v>
       </c>
       <c r="N78" t="n">
-        <v>2184.58</v>
+        <v>1676.36</v>
       </c>
       <c r="O78" t="n">
-        <v>0.0294</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>148357.67</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -6488,11 +6488,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>263589911</t>
+          <t>891380562</t>
         </is>
       </c>
       <c r="E79" s="1" t="n">
-        <v>33881</v>
+        <v>31635</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Segurança</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6520,20 +6520,20 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L79" s="1" t="n">
-        <v>44566</v>
+        <v>43955</v>
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
-        <v>4627.61</v>
+        <v>2294.12</v>
       </c>
       <c r="O79" t="n">
-        <v>0.0197</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>51493.59</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -6565,11 +6565,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>615606709</t>
+          <t>520860274</t>
         </is>
       </c>
       <c r="E80" s="1" t="n">
-        <v>30416</v>
+        <v>30882</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Estoquista</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6597,14 +6597,14 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L80" s="1" t="n">
-        <v>44171</v>
+        <v>45574</v>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
-        <v>2217.84</v>
+        <v>1929.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -6642,11 +6642,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>357689890</t>
+          <t>41166881</t>
         </is>
       </c>
       <c r="E81" s="1" t="n">
-        <v>33707</v>
+        <v>32488</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -6677,17 +6677,17 @@
         <v>14</v>
       </c>
       <c r="L81" s="1" t="n">
-        <v>43292</v>
+        <v>45711</v>
       </c>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
-        <v>1908.97</v>
+        <v>2262.31</v>
       </c>
       <c r="O81" t="n">
-        <v>0.0211</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>111345.27</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -6719,11 +6719,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>536926061</t>
+          <t>713346101</t>
         </is>
       </c>
       <c r="E82" s="1" t="n">
-        <v>24475</v>
+        <v>35464</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6751,20 +6751,20 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L82" s="1" t="n">
-        <v>43157</v>
+        <v>44480</v>
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="n">
-        <v>2120.87</v>
+        <v>6170.83</v>
       </c>
       <c r="O82" t="n">
-        <v>0.0182</v>
+        <v>0.0195</v>
       </c>
       <c r="P82" t="n">
-        <v>49804.81</v>
+        <v>32970.87</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -6796,11 +6796,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>406155255</t>
+          <t>84116113</t>
         </is>
       </c>
       <c r="E83" s="1" t="n">
-        <v>26197</v>
+        <v>31666</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Estoquista</t>
+          <t>Subgerente</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -6828,14 +6828,14 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L83" s="1" t="n">
-        <v>43242</v>
+        <v>44401</v>
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="n">
-        <v>1966.33</v>
+        <v>3580.38</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -6873,11 +6873,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>96125879</t>
+          <t>785395857</t>
         </is>
       </c>
       <c r="E84" s="1" t="n">
-        <v>31911</v>
+        <v>37950</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Auxiliar de Limpeza</t>
+          <t>Segurança</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -6908,11 +6908,11 @@
         <v>9</v>
       </c>
       <c r="L84" s="1" t="n">
-        <v>43868</v>
+        <v>43922</v>
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="n">
-        <v>1690.55</v>
+        <v>2108.66</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -6950,11 +6950,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>159413286</t>
+          <t>522374832</t>
         </is>
       </c>
       <c r="E85" s="1" t="n">
-        <v>24456</v>
+        <v>29980</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Subgerente</t>
+          <t>Segurança</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -6982,14 +6982,14 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L85" s="1" t="n">
-        <v>43553</v>
+        <v>43292</v>
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
-        <v>3540.01</v>
+        <v>2125.07</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -7027,11 +7027,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>19760099</t>
+          <t>810718317</t>
         </is>
       </c>
       <c r="E86" s="1" t="n">
-        <v>27457</v>
+        <v>38332</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Estoquista</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7059,20 +7059,20 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L86" s="1" t="n">
-        <v>45117</v>
+        <v>45315</v>
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="n">
-        <v>5167.42</v>
+        <v>2163.06</v>
       </c>
       <c r="O86" t="n">
-        <v>0.0189</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>145762.61</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -7104,11 +7104,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>981797229</t>
+          <t>536926061</t>
         </is>
       </c>
       <c r="E87" s="1" t="n">
-        <v>30061</v>
+        <v>24475</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7136,20 +7136,20 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L87" s="1" t="n">
-        <v>44663</v>
+        <v>45098</v>
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
-        <v>1859.85</v>
+        <v>6175.38</v>
       </c>
       <c r="O87" t="n">
-        <v>0.0305</v>
+        <v>0.0146</v>
       </c>
       <c r="P87" t="n">
-        <v>130013.82</v>
+        <v>72755.55</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -7181,11 +7181,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>856594822</t>
+          <t>406155255</t>
         </is>
       </c>
       <c r="E88" s="1" t="n">
-        <v>26204</v>
+        <v>26197</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Subgerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -7216,17 +7216,17 @@
         <v>2</v>
       </c>
       <c r="L88" s="1" t="n">
-        <v>44631</v>
+        <v>45925</v>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="n">
-        <v>3622.95</v>
+        <v>1747.38</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>0.0105</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>144183.32</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -7258,11 +7258,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>839191591</t>
+          <t>814427815</t>
         </is>
       </c>
       <c r="E89" s="1" t="n">
-        <v>28990</v>
+        <v>27167</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7290,14 +7290,14 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L89" s="1" t="n">
-        <v>44857</v>
+        <v>45525</v>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
-        <v>1804.09</v>
+        <v>2092.39</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -7335,11 +7335,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>367809382</t>
+          <t>59595946</t>
         </is>
       </c>
       <c r="E90" s="1" t="n">
-        <v>26590</v>
+        <v>30122</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Auxiliar de Limpeza</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7367,20 +7367,20 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L90" s="1" t="n">
-        <v>45846</v>
+        <v>43186</v>
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="n">
-        <v>1922.95</v>
+        <v>1775.02</v>
       </c>
       <c r="O90" t="n">
-        <v>0.0156</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>106968.65</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -7412,11 +7412,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>17888295</t>
+          <t>19760099</t>
         </is>
       </c>
       <c r="E91" s="1" t="n">
-        <v>33574</v>
+        <v>27457</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Segurança</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7444,20 +7444,20 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L91" s="1" t="n">
-        <v>45572</v>
+        <v>44706</v>
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
-        <v>2010.08</v>
+        <v>2019.18</v>
       </c>
       <c r="O91" t="n">
-        <v>0.0308</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>158614.11</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -7489,11 +7489,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>270629447</t>
+          <t>733565411</t>
         </is>
       </c>
       <c r="E92" s="1" t="n">
-        <v>29679</v>
+        <v>36780</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Estoquista</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -7521,22 +7521,22 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L92" s="1" t="n">
-        <v>43732</v>
+        <v>44725</v>
       </c>
       <c r="M92" s="1" t="n">
-        <v>44058</v>
+        <v>45175</v>
       </c>
       <c r="N92" t="n">
-        <v>2026</v>
+        <v>2448.31</v>
       </c>
       <c r="O92" t="n">
-        <v>0.0122</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>105781.11</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -7568,11 +7568,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>570986998</t>
+          <t>129744429</t>
         </is>
       </c>
       <c r="E93" s="1" t="n">
-        <v>34828</v>
+        <v>27899</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -7600,20 +7600,20 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L93" s="1" t="n">
-        <v>44120</v>
+        <v>44498</v>
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
-        <v>2175.82</v>
+        <v>2249</v>
       </c>
       <c r="O93" t="n">
-        <v>0.0302</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>35399.66</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -7645,11 +7645,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>964563744</t>
+          <t>333625075</t>
         </is>
       </c>
       <c r="E94" s="1" t="n">
-        <v>30526</v>
+        <v>31085</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Segurança</t>
+          <t>Subgerente</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -7677,14 +7677,14 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L94" s="1" t="n">
-        <v>43913</v>
+        <v>45562</v>
       </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
-        <v>2534.04</v>
+        <v>4425.98</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -7722,11 +7722,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>820128930</t>
+          <t>570903366</t>
         </is>
       </c>
       <c r="E95" s="1" t="n">
-        <v>31149</v>
+        <v>26590</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Subgerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -7754,20 +7754,20 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L95" s="1" t="n">
-        <v>44810</v>
+        <v>44450</v>
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
-        <v>3450.59</v>
+        <v>1922.95</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>0.0311</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>106968.65</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -7799,11 +7799,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>990893077</t>
+          <t>17888295</t>
         </is>
       </c>
       <c r="E96" s="1" t="n">
-        <v>26336</v>
+        <v>33574</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -7831,20 +7831,20 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L96" s="1" t="n">
-        <v>44819</v>
+        <v>45572</v>
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
-        <v>1899.12</v>
+        <v>5592.25</v>
       </c>
       <c r="O96" t="n">
-        <v>0.0211</v>
+        <v>0.0154</v>
       </c>
       <c r="P96" t="n">
-        <v>134590.37</v>
+        <v>158614.11</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -7876,11 +7876,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>977705801</t>
+          <t>927168364</t>
         </is>
       </c>
       <c r="E97" s="1" t="n">
-        <v>36923</v>
+        <v>26800</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Auxiliar de Limpeza</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -7908,14 +7908,14 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L97" s="1" t="n">
-        <v>43237</v>
+        <v>43732</v>
       </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
-        <v>1749.33</v>
+        <v>2136.41</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -7953,11 +7953,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>220259674</t>
+          <t>252446167</t>
         </is>
       </c>
       <c r="E98" s="1" t="n">
-        <v>26842</v>
+        <v>32954</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Estoquista</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -7985,22 +7985,22 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L98" s="1" t="n">
-        <v>45329</v>
+        <v>43543</v>
       </c>
       <c r="M98" s="1" t="n">
-        <v>45827</v>
+        <v>45544</v>
       </c>
       <c r="N98" t="n">
-        <v>1738.61</v>
+        <v>2016.52</v>
       </c>
       <c r="O98" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>134914.66</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -8032,11 +8032,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>369507984</t>
+          <t>415120538</t>
         </is>
       </c>
       <c r="E99" s="1" t="n">
-        <v>28717</v>
+        <v>32776</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Nutricionista</t>
+          <t>Segurança</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8064,14 +8064,14 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L99" s="1" t="n">
-        <v>43169</v>
+        <v>45994</v>
       </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="n">
-        <v>3481.91</v>
+        <v>1769.33</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -8109,11 +8109,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>680799660</t>
+          <t>964563744</t>
         </is>
       </c>
       <c r="E100" s="1" t="n">
-        <v>29946</v>
+        <v>30526</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8141,14 +8141,14 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L100" s="1" t="n">
-        <v>44900</v>
+        <v>43913</v>
       </c>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
-        <v>2183.71</v>
+        <v>2163.36</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -8186,11 +8186,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>727154197</t>
+          <t>515848872</t>
         </is>
       </c>
       <c r="E101" s="1" t="n">
-        <v>37983</v>
+        <v>36216</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -8218,20 +8218,20 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L101" s="1" t="n">
-        <v>44489</v>
+        <v>44810</v>
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
-        <v>5298.9</v>
+        <v>1968.39</v>
       </c>
       <c r="O101" t="n">
-        <v>0.0164</v>
+        <v>0.0307</v>
       </c>
       <c r="P101" t="n">
-        <v>72861.63</v>
+        <v>140233.21</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -8263,11 +8263,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>235291827</t>
+          <t>244823056</t>
         </is>
       </c>
       <c r="E102" s="1" t="n">
-        <v>31029</v>
+        <v>30193</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8295,20 +8295,20 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L102" s="1" t="n">
-        <v>45871</v>
+        <v>45694</v>
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="n">
-        <v>1821.4</v>
+        <v>1840.25</v>
       </c>
       <c r="O102" t="n">
-        <v>0.0154</v>
+        <v>0.0354</v>
       </c>
       <c r="P102" t="n">
-        <v>116138.32</v>
+        <v>25851.17</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -8340,11 +8340,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>413725631</t>
+          <t>858660636</t>
         </is>
       </c>
       <c r="E103" s="1" t="n">
-        <v>24771</v>
+        <v>27069</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Subgerente</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8372,20 +8372,20 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L103" s="1" t="n">
-        <v>44812</v>
+        <v>43721</v>
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
-        <v>2027.71</v>
+        <v>3222.89</v>
       </c>
       <c r="O103" t="n">
-        <v>0.0333</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>87425.83</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -8417,11 +8417,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>820198060</t>
+          <t>678265670</t>
         </is>
       </c>
       <c r="E104" s="1" t="n">
-        <v>32218</v>
+        <v>27907</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8449,20 +8449,20 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L104" s="1" t="n">
-        <v>43388</v>
+        <v>43971</v>
       </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="n">
-        <v>2155.72</v>
+        <v>1866.85</v>
       </c>
       <c r="O104" t="n">
-        <v>0.0329</v>
+        <v>0.0363</v>
       </c>
       <c r="P104" t="n">
-        <v>140185.41</v>
+        <v>56862.74</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -8494,11 +8494,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>386070714</t>
+          <t>986459835</t>
         </is>
       </c>
       <c r="E105" s="1" t="n">
-        <v>34734</v>
+        <v>32118</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8526,20 +8526,20 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L105" s="1" t="n">
-        <v>43372</v>
+        <v>43646</v>
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="n">
-        <v>2111.21</v>
+        <v>1913.36</v>
       </c>
       <c r="O105" t="n">
-        <v>0.0399</v>
+        <v>0.017</v>
       </c>
       <c r="P105" t="n">
-        <v>62638.33</v>
+        <v>158654.57</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -8571,11 +8571,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>150416922</t>
+          <t>39961414</t>
         </is>
       </c>
       <c r="E106" s="1" t="n">
-        <v>32555</v>
+        <v>26543</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Repositor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -8603,20 +8603,20 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L106" s="1" t="n">
-        <v>43911</v>
+        <v>45053</v>
       </c>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="n">
-        <v>2148.54</v>
+        <v>5478.29</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>66648.13</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -8648,11 +8648,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>966509459</t>
+          <t>757362633</t>
         </is>
       </c>
       <c r="E107" s="1" t="n">
-        <v>33549</v>
+        <v>27029</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8680,20 +8680,20 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L107" s="1" t="n">
-        <v>45736</v>
+        <v>44554</v>
       </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="n">
-        <v>1955.28</v>
+        <v>2037.55</v>
       </c>
       <c r="O107" t="n">
-        <v>0.0383</v>
+        <v>0.0116</v>
       </c>
       <c r="P107" t="n">
-        <v>26759.32</v>
+        <v>80084.82000000001</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -8725,11 +8725,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>21025374</t>
+          <t>677015569</t>
         </is>
       </c>
       <c r="E108" s="1" t="n">
-        <v>29155</v>
+        <v>36658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -8757,20 +8757,20 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L108" s="1" t="n">
-        <v>45965</v>
+        <v>43881</v>
       </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="n">
-        <v>1969.96</v>
+        <v>1931.21</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>0.0353</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>153797.67</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -8802,11 +8802,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>346404685</t>
+          <t>703342789</t>
         </is>
       </c>
       <c r="E109" s="1" t="n">
-        <v>35659</v>
+        <v>29833</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8834,20 +8834,20 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L109" s="1" t="n">
-        <v>45432</v>
+        <v>44169</v>
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="n">
-        <v>5712.89</v>
+        <v>5366.71</v>
       </c>
       <c r="O109" t="n">
-        <v>0.0104</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="P109" t="n">
-        <v>84032.95</v>
+        <v>159476.88</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -8879,11 +8879,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>59567894</t>
+          <t>53674351</t>
         </is>
       </c>
       <c r="E110" s="1" t="n">
-        <v>24803</v>
+        <v>25837</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Estoquista</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -8911,20 +8911,20 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L110" s="1" t="n">
-        <v>44291</v>
+        <v>43671</v>
       </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="n">
-        <v>1831.86</v>
+        <v>2435.53</v>
       </c>
       <c r="O110" t="n">
-        <v>0.0172</v>
+        <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>139714.43</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -8956,11 +8956,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>425450650</t>
+          <t>820275626</t>
         </is>
       </c>
       <c r="E111" s="1" t="n">
-        <v>26938</v>
+        <v>29785</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Auxiliar de Limpeza</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -8988,20 +8988,20 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L111" s="1" t="n">
-        <v>44129</v>
+        <v>43572</v>
       </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="n">
-        <v>1948.62</v>
+        <v>1483.53</v>
       </c>
       <c r="O111" t="n">
-        <v>0.0392</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>80404.34</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -9033,11 +9033,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>114491506</t>
+          <t>164180171</t>
         </is>
       </c>
       <c r="E112" s="1" t="n">
-        <v>32446</v>
+        <v>38085</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Segurança</t>
+          <t>Estoquista</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -9065,14 +9065,14 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L112" s="1" t="n">
-        <v>44592</v>
+        <v>43871</v>
       </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="n">
-        <v>2561.59</v>
+        <v>2405.89</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -9110,11 +9110,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>364078801</t>
+          <t>55354610</t>
         </is>
       </c>
       <c r="E113" s="1" t="n">
-        <v>24400</v>
+        <v>23944</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -9142,20 +9142,20 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L113" s="1" t="n">
-        <v>44226</v>
+        <v>43165</v>
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="n">
-        <v>1830.79</v>
+        <v>1853.54</v>
       </c>
       <c r="O113" t="n">
-        <v>0.0384</v>
+        <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>64762.6</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -9187,11 +9187,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>758478319</t>
+          <t>21025374</t>
         </is>
       </c>
       <c r="E114" s="1" t="n">
-        <v>28479</v>
+        <v>29155</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -9219,20 +9219,20 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L114" s="1" t="n">
-        <v>44209</v>
+        <v>45965</v>
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="n">
-        <v>1940.4</v>
+        <v>1969.96</v>
       </c>
       <c r="O114" t="n">
-        <v>0.0167</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>140060.1</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -9264,11 +9264,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>860103522</t>
+          <t>490739429</t>
         </is>
       </c>
       <c r="E115" s="1" t="n">
-        <v>33792</v>
+        <v>24119</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Repositor</t>
+          <t>Estoquista</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9296,14 +9296,14 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L115" s="1" t="n">
-        <v>43606</v>
+        <v>45432</v>
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
-        <v>2150.16</v>
+        <v>2162.36</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -9341,11 +9341,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>48668610</t>
+          <t>814366345</t>
         </is>
       </c>
       <c r="E116" s="1" t="n">
-        <v>29896</v>
+        <v>27406</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -9373,22 +9373,22 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L116" s="1" t="n">
-        <v>45338</v>
+        <v>43861</v>
       </c>
       <c r="M116" s="1" t="n">
-        <v>45720</v>
+        <v>45097</v>
       </c>
       <c r="N116" t="n">
-        <v>6045.91</v>
+        <v>1944.23</v>
       </c>
       <c r="O116" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>94797.19</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -9420,11 +9420,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>68919120</t>
+          <t>68911495</t>
         </is>
       </c>
       <c r="E117" s="1" t="n">
-        <v>24815</v>
+        <v>29336</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Repositor</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -9452,20 +9452,20 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L117" s="1" t="n">
-        <v>45835</v>
+        <v>45299</v>
       </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="n">
-        <v>1978.85</v>
+        <v>1985.98</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>0.0224</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>156202.79</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -9497,11 +9497,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>543473542</t>
+          <t>846874642</t>
         </is>
       </c>
       <c r="E118" s="1" t="n">
-        <v>27020</v>
+        <v>24553</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Auxiliar de Limpeza</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -9529,14 +9529,14 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L118" s="1" t="n">
-        <v>44947</v>
+        <v>44663</v>
       </c>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="n">
-        <v>1469.1</v>
+        <v>2270.54</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -9574,11 +9574,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>136066416</t>
+          <t>108492927</t>
         </is>
       </c>
       <c r="E119" s="1" t="n">
-        <v>25231</v>
+        <v>33781</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Segurança</t>
+          <t>Auxiliar de Limpeza</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -9606,14 +9606,14 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L119" s="1" t="n">
-        <v>45818</v>
+        <v>45647</v>
       </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="n">
-        <v>1952.34</v>
+        <v>1794.59</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -9651,11 +9651,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>310875080</t>
+          <t>364078801</t>
         </is>
       </c>
       <c r="E120" s="1" t="n">
-        <v>31120</v>
+        <v>24400</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Segurança</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -9683,20 +9683,20 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L120" s="1" t="n">
-        <v>44232</v>
+        <v>44436</v>
       </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="n">
-        <v>1995.7</v>
+        <v>1935.42</v>
       </c>
       <c r="O120" t="n">
-        <v>0.0284</v>
+        <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>30599.43</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -9728,11 +9728,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>807868815</t>
+          <t>967383642</t>
         </is>
       </c>
       <c r="E121" s="1" t="n">
-        <v>34146</v>
+        <v>29769</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -9760,20 +9760,20 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L121" s="1" t="n">
-        <v>43103</v>
+        <v>44115</v>
       </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="n">
-        <v>2346.58</v>
+        <v>2128.26</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>0.0283</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>40164.25</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -9805,11 +9805,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>795035337</t>
+          <t>860103522</t>
         </is>
       </c>
       <c r="E122" s="1" t="n">
-        <v>23980</v>
+        <v>33792</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Subgerente</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -9840,13 +9840,13 @@
         <v>12</v>
       </c>
       <c r="L122" s="1" t="n">
-        <v>44490</v>
+        <v>43283</v>
       </c>
       <c r="M122" s="1" t="n">
-        <v>44591</v>
+        <v>43971</v>
       </c>
       <c r="N122" t="n">
-        <v>4478.61</v>
+        <v>2340.19</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -9884,11 +9884,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>987667510</t>
+          <t>292967637</t>
         </is>
       </c>
       <c r="E123" s="1" t="n">
-        <v>37811</v>
+        <v>34848</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Repositor</t>
+          <t>Segurança</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -9916,14 +9916,14 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L123" s="1" t="n">
-        <v>45382</v>
+        <v>45338</v>
       </c>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="n">
-        <v>2133.27</v>
+        <v>1964.75</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -9961,11 +9961,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>396287234</t>
+          <t>48668610</t>
         </is>
       </c>
       <c r="E124" s="1" t="n">
-        <v>35371</v>
+        <v>29896</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -9993,20 +9993,20 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L124" s="1" t="n">
-        <v>43972</v>
+        <v>45441</v>
       </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="n">
-        <v>4887.12</v>
+        <v>2151.85</v>
       </c>
       <c r="O124" t="n">
-        <v>0.018</v>
+        <v>0.0359</v>
       </c>
       <c r="P124" t="n">
-        <v>68163.71000000001</v>
+        <v>94797.19</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -10038,11 +10038,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>11854915</t>
+          <t>47798960</t>
         </is>
       </c>
       <c r="E125" s="1" t="n">
-        <v>31302</v>
+        <v>35542</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -10070,16 +10070,16 @@
         </is>
       </c>
       <c r="K125" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L125" s="1" t="n">
-        <v>43911</v>
+        <v>45835</v>
       </c>
       <c r="M125" s="1" t="n">
-        <v>44056</v>
+        <v>46005</v>
       </c>
       <c r="N125" t="n">
-        <v>1959.55</v>
+        <v>2088.7</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -10117,11 +10117,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>652007702</t>
+          <t>543473542</t>
         </is>
       </c>
       <c r="E126" s="1" t="n">
-        <v>27588</v>
+        <v>27020</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Subgerente</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -10149,14 +10149,14 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L126" s="1" t="n">
-        <v>44034</v>
+        <v>44947</v>
       </c>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="n">
-        <v>4236.47</v>
+        <v>1832.74</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -10194,11 +10194,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>923236111</t>
+          <t>140459667</t>
         </is>
       </c>
       <c r="E127" s="1" t="n">
-        <v>31650</v>
+        <v>34550</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10226,22 +10226,22 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>45778</v>
+        <v>45818</v>
       </c>
       <c r="M127" s="1" t="n">
-        <v>45947</v>
+        <v>46020</v>
       </c>
       <c r="N127" t="n">
-        <v>1948.12</v>
+        <v>1832.38</v>
       </c>
       <c r="O127" t="n">
-        <v>0.0339</v>
+        <v>0.037</v>
       </c>
       <c r="P127" t="n">
-        <v>51842.21</v>
+        <v>107804.37</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -10273,11 +10273,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>722378324</t>
+          <t>310875080</t>
         </is>
       </c>
       <c r="E128" s="1" t="n">
-        <v>35704</v>
+        <v>31120</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Segurança</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -10305,14 +10305,14 @@
         </is>
       </c>
       <c r="K128" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L128" s="1" t="n">
-        <v>43340</v>
+        <v>43371</v>
       </c>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="n">
-        <v>2464.33</v>
+        <v>2154.84</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -10350,11 +10350,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>645495533</t>
+          <t>807868815</t>
         </is>
       </c>
       <c r="E129" s="1" t="n">
-        <v>28304</v>
+        <v>34146</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10382,20 +10382,20 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L129" s="1" t="n">
-        <v>43903</v>
+        <v>43466</v>
       </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="n">
-        <v>1778.4</v>
+        <v>2155.49</v>
       </c>
       <c r="O129" t="n">
-        <v>0.0112</v>
+        <v>0.0165</v>
       </c>
       <c r="P129" t="n">
-        <v>131682.1</v>
+        <v>112971.87</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -10427,11 +10427,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>347772596</t>
+          <t>795035337</t>
         </is>
       </c>
       <c r="E130" s="1" t="n">
-        <v>26894</v>
+        <v>23980</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Segurança</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -10459,14 +10459,14 @@
         </is>
       </c>
       <c r="K130" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L130" s="1" t="n">
-        <v>44631</v>
+        <v>45160</v>
       </c>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="n">
-        <v>1787.68</v>
+        <v>2191.77</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -10504,11 +10504,11 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>62705619</t>
+          <t>987667510</t>
         </is>
       </c>
       <c r="E131" s="1" t="n">
-        <v>24887</v>
+        <v>37811</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Estoquista</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -10539,17 +10539,17 @@
         <v>1</v>
       </c>
       <c r="L131" s="1" t="n">
-        <v>45887</v>
+        <v>45382</v>
       </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="n">
-        <v>5334.81</v>
+        <v>2506.57</v>
       </c>
       <c r="O131" t="n">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>124330.93</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -10581,11 +10581,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>629281685</t>
+          <t>519879493</t>
         </is>
       </c>
       <c r="E132" s="1" t="n">
-        <v>30021</v>
+        <v>37170</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Caixa</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -10613,20 +10613,20 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L132" s="1" t="n">
-        <v>45353</v>
+        <v>43972</v>
       </c>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="n">
-        <v>6151.27</v>
+        <v>1967.2</v>
       </c>
       <c r="O132" t="n">
-        <v>0.0116</v>
+        <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>82649.38</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -10658,11 +10658,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>578589304</t>
+          <t>709434091</t>
         </is>
       </c>
       <c r="E133" s="1" t="n">
-        <v>28548</v>
+        <v>33906</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Auxiliar de Limpeza</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -10690,14 +10690,14 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L133" s="1" t="n">
-        <v>45728</v>
+        <v>44757</v>
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
-        <v>1871.35</v>
+        <v>1550.94</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -10735,11 +10735,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>293910653</t>
+          <t>78357327</t>
         </is>
       </c>
       <c r="E134" s="1" t="n">
-        <v>31678</v>
+        <v>25276</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Repositor</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -10767,20 +10767,20 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L134" s="1" t="n">
-        <v>44694</v>
+        <v>45763</v>
       </c>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="n">
-        <v>2152.24</v>
+        <v>1759.9</v>
       </c>
       <c r="O134" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>104635.53</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -10812,11 +10812,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>34643087</t>
+          <t>430866677</t>
         </is>
       </c>
       <c r="E135" s="1" t="n">
-        <v>27594</v>
+        <v>29710</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Auxiliar de Limpeza</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -10844,20 +10844,20 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L135" s="1" t="n">
-        <v>45071</v>
+        <v>44679</v>
       </c>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="n">
-        <v>1601.03</v>
+        <v>1997.55</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>0.0339</v>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>69235.84</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -10889,11 +10889,11 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>442433538</t>
+          <t>432025352</t>
         </is>
       </c>
       <c r="E136" s="1" t="n">
-        <v>24275</v>
+        <v>32174</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10921,20 +10921,20 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L136" s="1" t="n">
-        <v>45947</v>
+        <v>43329</v>
       </c>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="n">
-        <v>6154.76</v>
+        <v>5252.51</v>
       </c>
       <c r="O136" t="n">
-        <v>0.0165</v>
+        <v>0.0143</v>
       </c>
       <c r="P136" t="n">
-        <v>172466.73</v>
+        <v>139650.06</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -10966,11 +10966,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>232370516</t>
+          <t>179648480</t>
         </is>
       </c>
       <c r="E137" s="1" t="n">
-        <v>34130</v>
+        <v>25717</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Subgerente</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -10998,20 +10998,20 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L137" s="1" t="n">
-        <v>44577</v>
+        <v>43903</v>
       </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="n">
-        <v>1762.62</v>
+        <v>3360.12</v>
       </c>
       <c r="O137" t="n">
-        <v>0.0251</v>
+        <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>147186.01</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -11043,11 +11043,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>947054430</t>
+          <t>64453772</t>
         </is>
       </c>
       <c r="E138" s="1" t="n">
-        <v>36446</v>
+        <v>25273</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -11075,20 +11075,20 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L138" s="1" t="n">
-        <v>45805</v>
+        <v>45802</v>
       </c>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="n">
-        <v>4950.82</v>
+        <v>2042.35</v>
       </c>
       <c r="O138" t="n">
-        <v>0.0166</v>
+        <v>0.0214</v>
       </c>
       <c r="P138" t="n">
-        <v>83718.82000000001</v>
+        <v>38152.64</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -11120,11 +11120,11 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>765164414</t>
+          <t>195862208</t>
         </is>
       </c>
       <c r="E139" s="1" t="n">
-        <v>31361</v>
+        <v>37494</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11152,20 +11152,20 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L139" s="1" t="n">
-        <v>43505</v>
+        <v>45887</v>
       </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="n">
-        <v>1828.07</v>
+        <v>1952.77</v>
       </c>
       <c r="O139" t="n">
-        <v>0.0181</v>
+        <v>0.0254</v>
       </c>
       <c r="P139" t="n">
-        <v>99615.28999999999</v>
+        <v>84766.12</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -11197,11 +11197,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>247681817</t>
+          <t>52666361</t>
         </is>
       </c>
       <c r="E140" s="1" t="n">
-        <v>34940</v>
+        <v>31890</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Nutricionista</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -11229,20 +11229,20 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L140" s="1" t="n">
-        <v>44446</v>
+        <v>45283</v>
       </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="n">
-        <v>1805.63</v>
+        <v>3968.66</v>
       </c>
       <c r="O140" t="n">
-        <v>0.0364</v>
+        <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>38140.6</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -11274,11 +11274,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>663231325</t>
+          <t>952030829</t>
         </is>
       </c>
       <c r="E141" s="1" t="n">
-        <v>25980</v>
+        <v>36097</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -11306,20 +11306,20 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L141" s="1" t="n">
-        <v>45069</v>
+        <v>45728</v>
       </c>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="n">
-        <v>1765.28</v>
+        <v>6104.76</v>
       </c>
       <c r="O141" t="n">
-        <v>0.0399</v>
+        <v>0.0107</v>
       </c>
       <c r="P141" t="n">
-        <v>39289.23</v>
+        <v>118804.08</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -11351,11 +11351,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>54854168</t>
+          <t>396086837</t>
         </is>
       </c>
       <c r="E142" s="1" t="n">
-        <v>36738</v>
+        <v>25742</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -11383,20 +11383,20 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L142" s="1" t="n">
-        <v>43463</v>
+        <v>44992</v>
       </c>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="n">
-        <v>5854.47</v>
+        <v>1952.87</v>
       </c>
       <c r="O142" t="n">
-        <v>0.0091</v>
+        <v>0.0371</v>
       </c>
       <c r="P142" t="n">
-        <v>124205.99</v>
+        <v>146211.3</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -11428,11 +11428,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>563484536</t>
+          <t>442433538</t>
         </is>
       </c>
       <c r="E143" s="1" t="n">
-        <v>30067</v>
+        <v>24275</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -11460,20 +11460,20 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>43863</v>
+        <v>44561</v>
       </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="n">
-        <v>5787.87</v>
+        <v>2082.13</v>
       </c>
       <c r="O143" t="n">
-        <v>0.0089</v>
+        <v>0.0121</v>
       </c>
       <c r="P143" t="n">
-        <v>25184.32</v>
+        <v>50765.84</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -11505,11 +11505,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>444301891</t>
+          <t>232370516</t>
         </is>
       </c>
       <c r="E144" s="1" t="n">
-        <v>32634</v>
+        <v>34130</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Segurança</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -11537,20 +11537,20 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L144" s="1" t="n">
-        <v>45396</v>
+        <v>44577</v>
       </c>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="n">
-        <v>2084.77</v>
+        <v>1762.62</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>0.0251</v>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>147186.01</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -11582,11 +11582,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>23320941</t>
+          <t>614830048</t>
         </is>
       </c>
       <c r="E145" s="1" t="n">
-        <v>36349</v>
+        <v>36446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11617,19 +11617,19 @@
         <v>14</v>
       </c>
       <c r="L145" s="1" t="n">
-        <v>44237</v>
+        <v>45805</v>
       </c>
       <c r="M145" s="1" t="n">
-        <v>44889</v>
+        <v>45936</v>
       </c>
       <c r="N145" t="n">
-        <v>2021.64</v>
+        <v>1894.6</v>
       </c>
       <c r="O145" t="n">
-        <v>0.0332</v>
+        <v>0.0139</v>
       </c>
       <c r="P145" t="n">
-        <v>42969.62</v>
+        <v>149190.3</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -11661,11 +11661,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>611148047</t>
+          <t>765164414</t>
         </is>
       </c>
       <c r="E146" s="1" t="n">
-        <v>31949</v>
+        <v>31361</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11693,20 +11693,20 @@
         </is>
       </c>
       <c r="K146" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>43644</v>
+        <v>43505</v>
       </c>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="n">
-        <v>1974.47</v>
+        <v>1828.07</v>
       </c>
       <c r="O146" t="n">
-        <v>0.0116</v>
+        <v>0.0181</v>
       </c>
       <c r="P146" t="n">
-        <v>86241.66</v>
+        <v>99615.28999999999</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -11738,11 +11738,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>98024422</t>
+          <t>45809796</t>
         </is>
       </c>
       <c r="E147" s="1" t="n">
-        <v>31986</v>
+        <v>29758</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11770,22 +11770,22 @@
         </is>
       </c>
       <c r="K147" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>45715</v>
+        <v>44446</v>
       </c>
       <c r="M147" s="1" t="n">
-        <v>45846</v>
+        <v>45623</v>
       </c>
       <c r="N147" t="n">
-        <v>1839.22</v>
+        <v>1853</v>
       </c>
       <c r="O147" t="n">
-        <v>0.03</v>
+        <v>0.0192</v>
       </c>
       <c r="P147" t="n">
-        <v>153069.42</v>
+        <v>89380.42</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -11817,11 +11817,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>607954507</t>
+          <t>499146939</t>
         </is>
       </c>
       <c r="E148" s="1" t="n">
-        <v>30997</v>
+        <v>32139</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Repositor</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -11849,20 +11849,20 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>43704</v>
+        <v>45240</v>
       </c>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="n">
-        <v>2021.14</v>
+        <v>1752.92</v>
       </c>
       <c r="O148" t="n">
-        <v>0</v>
+        <v>0.0221</v>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>83241.35000000001</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -11894,11 +11894,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>384565814</t>
+          <t>54854168</t>
         </is>
       </c>
       <c r="E149" s="1" t="n">
-        <v>35527</v>
+        <v>36738</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Caixa</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -11926,20 +11926,20 @@
         </is>
       </c>
       <c r="K149" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>45358</v>
+        <v>43463</v>
       </c>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="n">
-        <v>1879.29</v>
+        <v>5854.47</v>
       </c>
       <c r="O149" t="n">
-        <v>0</v>
+        <v>0.0091</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>124205.99</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -11971,11 +11971,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>623425683</t>
+          <t>255536948</t>
         </is>
       </c>
       <c r="E150" s="1" t="n">
-        <v>24501</v>
+        <v>35481</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Vendedor</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -12003,22 +12003,22 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>45486</v>
+        <v>43863</v>
       </c>
       <c r="M150" s="1" t="n">
-        <v>45851</v>
+        <v>45147</v>
       </c>
       <c r="N150" t="n">
-        <v>5930.95</v>
+        <v>1769.27</v>
       </c>
       <c r="O150" t="n">
-        <v>0.0123</v>
+        <v>0.032</v>
       </c>
       <c r="P150" t="n">
-        <v>93156.21000000001</v>
+        <v>47487.66</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -12050,11 +12050,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>165322586</t>
+          <t>465467707</t>
         </is>
       </c>
       <c r="E151" s="1" t="n">
-        <v>26157</v>
+        <v>36561</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12082,20 +12082,20 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>43897</v>
+        <v>45396</v>
       </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="n">
-        <v>1815.05</v>
+        <v>2179.17</v>
       </c>
       <c r="O151" t="n">
-        <v>0.0238</v>
+        <v>0.0399</v>
       </c>
       <c r="P151" t="n">
-        <v>75394.07000000001</v>
+        <v>65711.87</v>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
